--- a/数据/20240629000323.xlsx
+++ b/数据/20240629000323.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\python\bilibili日V周刊\数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A79A8AD-7F30-49BD-8F54-F90AA8DEE9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F270D1-94E9-4BDD-A4FB-B5B328FFCB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2782" uniqueCount="2403">
   <si>
     <t>video_title</t>
   </si>
@@ -7244,6 +7244,23 @@
   <si>
     <t>なみぐる_namigroove</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BV1sS421o7sg</t>
+  </si>
+  <si>
+    <t>2024-06-28 19:00:00</t>
+  </si>
+  <si>
+    <t>COVER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>COVER / 沫尾 feat. KAITO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沫尾</t>
   </si>
 </sst>
 </file>
@@ -7633,7 +7650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L554"/>
+  <dimension ref="A1:L555"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="17.08984375" customWidth="1"/>
@@ -28691,6 +28708,44 @@
         <v>917</v>
       </c>
     </row>
+    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B555" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C555" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D555" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E555" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F555">
+        <v>1147</v>
+      </c>
+      <c r="G555">
+        <v>10</v>
+      </c>
+      <c r="H555">
+        <v>53</v>
+      </c>
+      <c r="I555">
+        <v>298</v>
+      </c>
+      <c r="J555">
+        <v>246</v>
+      </c>
+      <c r="K555">
+        <v>65</v>
+      </c>
+      <c r="L555">
+        <v>368</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
